--- a/data/source/weekly/cs-en-us-060pct.xlsx
+++ b/data/source/weekly/cs-en-us-060pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -881,8 +881,8 @@
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>-100</v>
       </c>
       <c r="N14" s="15">
         <v>-100</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="L15" s="15">
+        <v>300</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="15">
         <v>100</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="15">
-        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
         <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>40</v>
+        <v>-20</v>
       </c>
       <c r="I16" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K16" s="15">
-        <v>33.333333333333</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L16" s="15">
-        <v>-29.411764705882</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.846153846153</v>
+        <v>-58.064516129032</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.990825688073</v>
+        <v>-90.298507462686</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>113.333333333333</v>
+        <v>76.470588235294</v>
       </c>
       <c r="I17" s="14">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="J17" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K17" s="15">
-        <v>88.461538461538</v>
+        <v>93.333333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>48.484848484848</v>
+        <v>26.086956521739</v>
       </c>
       <c r="M17" s="15">
-        <v>276.923076923077</v>
+        <v>346.153846153846</v>
       </c>
       <c r="N17" s="15">
-        <v>-34.666666666666</v>
+        <v>-31.764705882352</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
         <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J18" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K18" s="15">
-        <v>-41.176470588235</v>
+        <v>-25</v>
       </c>
       <c r="L18" s="15">
-        <v>25</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-28.571428571428</v>
+        <v>7.142857142857</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.150442477876</v>
+        <v>-88.372093023255</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F19" s="14">
         <v>18</v>
       </c>
       <c r="G19" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H19" s="15">
-        <v>-18.181818181818</v>
+        <v>-10</v>
       </c>
       <c r="I19" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J19" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K19" s="15">
-        <v>-13.333333333333</v>
+        <v>-3.125</v>
       </c>
       <c r="L19" s="15">
-        <v>-29.729729729729</v>
+        <v>-26.190476190476</v>
       </c>
       <c r="M19" s="15">
-        <v>-43.478260869565</v>
+        <v>-44.642857142857</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.938775510204</v>
+        <v>-46.551724137931</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
         <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K20" s="15">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="L20" s="15">
-        <v>-10</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M20" s="15">
-        <v>-30.769230769230</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.666666666666</v>
+        <v>-91.935483870967</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>7.142857142857</v>
+        <v>31.25</v>
       </c>
       <c r="F21" s="17">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G21" s="17">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H21" s="18">
-        <v>11.290322580645</v>
+        <v>4.615384615384</v>
       </c>
       <c r="I21" s="17">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="J21" s="17">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="K21" s="18">
-        <v>18.681318681318</v>
+        <v>22.429906542056</v>
       </c>
       <c r="L21" s="18">
-        <v>1.886792452830</v>
+        <v>1.550387596899</v>
       </c>
       <c r="M21" s="18">
-        <v>-3.571428571428</v>
+        <v>2.34375</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.367614879649</v>
+        <v>-75.468164794007</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1207,10 +1207,10 @@
         <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
         <v>3</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
       <c r="E23" s="15">
-        <v>200</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H23" s="15">
-        <v>116.666666666667</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K23" s="15">
-        <v>63.636363636363</v>
+        <v>35.714285714285</v>
       </c>
       <c r="L23" s="15">
-        <v>-14.285714285714</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>-5</v>
+        <v>38.461538461538</v>
       </c>
       <c r="F24" s="14">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G24" s="14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H24" s="15">
-        <v>6.25</v>
+        <v>3.076923076923</v>
       </c>
       <c r="I24" s="14">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="J24" s="14">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K24" s="15">
-        <v>7.594936708860</v>
+        <v>11.956521739130</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.018348623853</v>
+        <v>-15.573770491803</v>
       </c>
       <c r="M24" s="15">
-        <v>-24.778761061946</v>
+        <v>-14.876033057851</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>6</v>
+      </c>
+      <c r="D25" s="14">
         <v>5</v>
       </c>
-      <c r="D25" s="14">
-        <v>8</v>
-      </c>
       <c r="E25" s="15">
-        <v>-37.5</v>
+        <v>20</v>
       </c>
       <c r="F25" s="14">
         <v>17</v>
       </c>
       <c r="G25" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H25" s="15">
-        <v>-15</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="I25" s="14">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J25" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K25" s="15">
-        <v>-12.5</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="L25" s="15">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
         <v>13</v>
       </c>
       <c r="E26" s="15">
+        <v>-15.384615384615</v>
+      </c>
+      <c r="F26" s="14">
+        <v>45</v>
+      </c>
+      <c r="G26" s="14">
+        <v>45</v>
+      </c>
+      <c r="H26" s="15">
         <v>0</v>
       </c>
-      <c r="F26" s="14">
-        <v>44</v>
-      </c>
-      <c r="G26" s="14">
-        <v>43</v>
-      </c>
-      <c r="H26" s="15">
-        <v>2.325581395348</v>
-      </c>
       <c r="I26" s="14">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="J26" s="14">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K26" s="15">
-        <v>-22.857142857142</v>
+        <v>-21.686746987951</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.285714285714</v>
+        <v>-15.584415584415</v>
       </c>
       <c r="M26" s="15">
-        <v>28.571428571428</v>
+        <v>47.727272727272</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
       </c>
       <c r="I28" s="14">
+        <v>9</v>
+      </c>
+      <c r="J28" s="14">
         <v>7</v>
       </c>
-      <c r="J28" s="14">
-        <v>6</v>
-      </c>
       <c r="K28" s="15">
-        <v>16.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L28" s="15">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>-100</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-060pct.xlsx
+++ b/data/source/weekly/cs-en-us-060pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -878,8 +878,8 @@
       <c r="K14" s="15">
         <v>-100</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="15">
+        <v>-100</v>
       </c>
       <c r="M14" s="15">
         <v>-100</v>
@@ -892,32 +892,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="15">
         <v>300</v>
@@ -926,7 +926,7 @@
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
         <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J16" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K16" s="15">
-        <v>18.181818181818</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.777777777777</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.064516129032</v>
+        <v>-51.515151515151</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.298507462686</v>
+        <v>-89.610389610389</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H17" s="15">
-        <v>76.470588235294</v>
+        <v>40.909090909090</v>
       </c>
       <c r="I17" s="14">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J17" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K17" s="15">
-        <v>93.333333333333</v>
+        <v>80.555555555555</v>
       </c>
       <c r="L17" s="15">
-        <v>26.086956521739</v>
+        <v>20.370370370370</v>
       </c>
       <c r="M17" s="15">
-        <v>346.153846153846</v>
+        <v>333.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-31.764705882352</v>
+        <v>-32.989690721649</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
-      </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
-      <c r="E18" s="15">
-        <v>33.333333333333</v>
+        <v>2</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
+        <v>7</v>
+      </c>
+      <c r="G18" s="14">
         <v>10</v>
       </c>
-      <c r="G18" s="14">
-        <v>14</v>
-      </c>
       <c r="H18" s="15">
-        <v>-28.571428571428</v>
+        <v>-30</v>
       </c>
       <c r="I18" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J18" s="14">
         <v>20</v>
       </c>
       <c r="K18" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="L18" s="15">
-        <v>66.666666666666</v>
+        <v>45.454545454545</v>
       </c>
       <c r="M18" s="15">
-        <v>7.142857142857</v>
+        <v>6.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.372093023255</v>
+        <v>-89.189189189189</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>8</v>
+      </c>
+      <c r="D19" s="14">
         <v>5</v>
       </c>
-      <c r="D19" s="14">
-        <v>2</v>
-      </c>
       <c r="E19" s="15">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F19" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G19" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H19" s="15">
-        <v>-10</v>
+        <v>10.526315789473</v>
       </c>
       <c r="I19" s="14">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J19" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.125</v>
+        <v>5.405405405405</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.190476190476</v>
+        <v>-20.408163265306</v>
       </c>
       <c r="M19" s="15">
-        <v>-44.642857142857</v>
+        <v>-39.0625</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.551724137931</v>
+        <v>-43.478260869565</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-66.666666666666</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J20" s="14">
         <v>8</v>
       </c>
       <c r="K20" s="15">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="L20" s="15">
-        <v>-23.076923076923</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>-23.076923076923</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.935483870967</v>
+        <v>-92.142857142857</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>31.25</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>4.615384615384</v>
+        <v>2.898550724637</v>
       </c>
       <c r="I21" s="17">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="J21" s="17">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="K21" s="18">
-        <v>22.429906542056</v>
+        <v>20.8</v>
       </c>
       <c r="L21" s="18">
-        <v>1.550387596899</v>
+        <v>-3.821656050955</v>
       </c>
       <c r="M21" s="18">
-        <v>2.34375</v>
+        <v>5.594405594405</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.468164794007</v>
+        <v>-75.407166123778</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
         <v>2</v>
       </c>
       <c r="J22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L22" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-66.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H23" s="15">
-        <v>-33.333333333333</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I23" s="14">
+        <v>23</v>
+      </c>
+      <c r="J23" s="14">
         <v>19</v>
       </c>
-      <c r="J23" s="14">
-        <v>14</v>
-      </c>
       <c r="K23" s="15">
-        <v>35.714285714285</v>
+        <v>21.052631578947</v>
       </c>
       <c r="L23" s="15">
-        <v>-13.636363636363</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="M23" s="15">
-        <v>90</v>
+        <v>76.923076923076</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>9</v>
+      </c>
+      <c r="D24" s="14">
         <v>18</v>
       </c>
-      <c r="D24" s="14">
-        <v>13</v>
-      </c>
       <c r="E24" s="15">
-        <v>38.461538461538</v>
+        <v>-50</v>
       </c>
       <c r="F24" s="14">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="G24" s="14">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H24" s="15">
-        <v>3.076923076923</v>
+        <v>-15.625</v>
       </c>
       <c r="I24" s="14">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="J24" s="14">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="K24" s="15">
-        <v>11.956521739130</v>
+        <v>2.727272727272</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.573770491803</v>
+        <v>-18.705035971223</v>
       </c>
       <c r="M24" s="15">
-        <v>-14.876033057851</v>
+        <v>-19.285714285714</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
+        <v>14</v>
+      </c>
+      <c r="G25" s="14">
         <v>17</v>
       </c>
-      <c r="G25" s="14">
-        <v>23</v>
-      </c>
       <c r="H25" s="15">
-        <v>-26.086956521739</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="I25" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J25" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.896551724137</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="L25" s="15">
-        <v>-25</v>
+        <v>-29.268292682926</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-15.384615384615</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G26" s="14">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>11.363636363636</v>
       </c>
       <c r="I26" s="14">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="J26" s="14">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K26" s="15">
-        <v>-21.686746987951</v>
+        <v>-16.304347826087</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.584415584415</v>
+        <v>-16.304347826087</v>
       </c>
       <c r="M26" s="15">
-        <v>47.727272727272</v>
+        <v>60.416666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>-20</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L27" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I28" s="14">
+        <v>8</v>
+      </c>
+      <c r="J28" s="14">
+        <v>8</v>
+      </c>
+      <c r="K28" s="15">
         <v>0</v>
       </c>
-      <c r="I28" s="14">
-        <v>9</v>
-      </c>
-      <c r="J28" s="14">
-        <v>7</v>
-      </c>
-      <c r="K28" s="15">
-        <v>28.571428571428</v>
-      </c>
       <c r="L28" s="15">
-        <v>200</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,31 +1484,31 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,23 +1525,23 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-060pct.xlsx
+++ b/data/source/weekly/cs-en-us-060pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -896,7 +896,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
         <v>-100</v>
@@ -905,19 +905,19 @@
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="15">
         <v>300</v>
@@ -926,7 +926,7 @@
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
         <v>3</v>
       </c>
-      <c r="D16" s="14">
-        <v>6</v>
-      </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-40</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J16" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>-5.882352941176</v>
+        <v>-10</v>
       </c>
       <c r="L16" s="15">
-        <v>-38.461538461538</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M16" s="15">
-        <v>-51.515151515151</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.610389610389</v>
+        <v>-89.655172413793</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>16.666666666666</v>
+        <v>266.666666666667</v>
       </c>
       <c r="F17" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G17" s="14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H17" s="15">
-        <v>40.909090909090</v>
+        <v>112.5</v>
       </c>
       <c r="I17" s="14">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="J17" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K17" s="15">
-        <v>80.555555555555</v>
+        <v>94.871794871794</v>
       </c>
       <c r="L17" s="15">
-        <v>20.370370370370</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>333.333333333333</v>
+        <v>322.222222222222</v>
       </c>
       <c r="N17" s="15">
-        <v>-32.989690721649</v>
+        <v>-29.629629629629</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K18" s="15">
-        <v>-20</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L18" s="15">
-        <v>45.454545454545</v>
+        <v>50</v>
       </c>
       <c r="M18" s="15">
-        <v>6.666666666666</v>
+        <v>-10</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.189189189189</v>
+        <v>-88.957055214723</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G19" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H19" s="15">
-        <v>10.526315789473</v>
+        <v>86.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="J19" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K19" s="15">
-        <v>5.405405405405</v>
+        <v>21.951219512195</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.408163265306</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="M19" s="15">
-        <v>-39.0625</v>
+        <v>-29.577464788732</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.478260869565</v>
+        <v>-35.064935064935</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I20" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="15">
-        <v>37.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-26.666666666666</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="M20" s="15">
-        <v>-26.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.142857142857</v>
+        <v>-92.638036809816</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>16.666666666666</v>
+        <v>80</v>
       </c>
       <c r="F21" s="17">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H21" s="18">
-        <v>2.898550724637</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="J21" s="17">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="K21" s="18">
-        <v>20.8</v>
+        <v>27.142857142857</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.821656050955</v>
+        <v>4.705882352941</v>
       </c>
       <c r="M21" s="18">
-        <v>5.594405594405</v>
+        <v>7.228915662650</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.407166123778</v>
+        <v>-74.314574314574</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
+        <v>2</v>
+      </c>
+      <c r="G22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
-      </c>
-      <c r="G22" s="14">
-        <v>2</v>
-      </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
         <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-20</v>
+        <v>200</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G23" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>-18.181818181818</v>
+        <v>10</v>
       </c>
       <c r="I23" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J23" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K23" s="15">
-        <v>21.052631578947</v>
+        <v>30</v>
       </c>
       <c r="L23" s="15">
-        <v>-14.814814814814</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M23" s="15">
-        <v>76.923076923076</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>-50</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="F24" s="14">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G24" s="14">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H24" s="15">
-        <v>-15.625</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I24" s="14">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="J24" s="14">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="K24" s="15">
-        <v>2.727272727272</v>
+        <v>0</v>
       </c>
       <c r="L24" s="15">
-        <v>-18.705035971223</v>
+        <v>-19.108280254777</v>
       </c>
       <c r="M24" s="15">
-        <v>-19.285714285714</v>
+        <v>-15.894039735099</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H25" s="15">
-        <v>-17.647058823529</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I25" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J25" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.451612903225</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="L25" s="15">
-        <v>-29.268292682926</v>
+        <v>-34.042553191489</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="F26" s="14">
         <v>49</v>
       </c>
       <c r="G26" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>11.363636363636</v>
+        <v>13.953488372093</v>
       </c>
       <c r="I26" s="14">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J26" s="14">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K26" s="15">
-        <v>-16.304347826087</v>
+        <v>-10</v>
       </c>
       <c r="L26" s="15">
-        <v>-16.304347826087</v>
+        <v>-15.094339622641</v>
       </c>
       <c r="M26" s="15">
-        <v>60.416666666666</v>
+        <v>60.714285714285</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,19 +1397,19 @@
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H27" s="15">
-        <v>-60</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-42.857142857142</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L27" s="15">
         <v>0</v>
@@ -1435,25 +1435,25 @@
         <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I28" s="14">
         <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L28" s="15">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-060pct.xlsx
+++ b/data/source/weekly/cs-en-us-060pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -905,22 +905,22 @@
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="L15" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -936,38 +936,38 @@
       <c r="C16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="14">
-        <v>3</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-33.333333333333</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-41.666666666666</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I16" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J16" s="14">
         <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.714285714285</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-52.631578947368</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.655172413793</v>
+        <v>-88.601036269430</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>266.666666666667</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F17" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G17" s="14">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>112.5</v>
+        <v>18.518518518518</v>
       </c>
       <c r="I17" s="14">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J17" s="14">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K17" s="15">
-        <v>94.871794871794</v>
+        <v>54.716981132075</v>
       </c>
       <c r="L17" s="15">
-        <v>33.333333333333</v>
+        <v>26.153846153846</v>
       </c>
       <c r="M17" s="15">
-        <v>322.222222222222</v>
+        <v>290.47619047619</v>
       </c>
       <c r="N17" s="15">
-        <v>-29.629629629629</v>
+        <v>-32.231404958677</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
         <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J18" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K18" s="15">
-        <v>-18.181818181818</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="L18" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.957055214723</v>
+        <v>-89.247311827957</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>175</v>
+        <v>12.5</v>
       </c>
       <c r="F19" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G19" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H19" s="15">
-        <v>86.666666666666</v>
+        <v>68.421052631578</v>
       </c>
       <c r="I19" s="14">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="J19" s="14">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K19" s="15">
-        <v>21.951219512195</v>
+        <v>18.367346938775</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.407407407407</v>
+        <v>-1.694915254237</v>
       </c>
       <c r="M19" s="15">
-        <v>-29.577464788732</v>
+        <v>-28.395061728395</v>
       </c>
       <c r="N19" s="15">
-        <v>-35.064935064935</v>
+        <v>-40.206185567010</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
         <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="14">
         <v>12</v>
       </c>
       <c r="J20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K20" s="15">
-        <v>33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="L20" s="15">
-        <v>-29.411764705882</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="M20" s="15">
-        <v>-33.333333333333</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.638036809816</v>
+        <v>-93.548387096774</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>80</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="F21" s="17">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G21" s="17">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="H21" s="18">
-        <v>33.333333333333</v>
+        <v>17.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="J21" s="17">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="K21" s="18">
-        <v>27.142857142857</v>
+        <v>19.277108433734</v>
       </c>
       <c r="L21" s="18">
-        <v>4.705882352941</v>
+        <v>3.664921465968</v>
       </c>
       <c r="M21" s="18">
-        <v>7.228915662650</v>
+        <v>3.664921465968</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.314574314574</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
+        <v>5</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>400</v>
+      </c>
+      <c r="F22" s="14">
+        <v>7</v>
+      </c>
+      <c r="G22" s="14">
         <v>2</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="14">
-        <v>2</v>
-      </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="I22" s="14">
+        <v>9</v>
+      </c>
+      <c r="J22" s="14">
         <v>4</v>
       </c>
-      <c r="J22" s="14">
-        <v>3</v>
-      </c>
       <c r="K22" s="15">
-        <v>33.333333333333</v>
+        <v>125</v>
       </c>
       <c r="L22" s="15">
-        <v>33.333333333333</v>
+        <v>80</v>
       </c>
       <c r="M22" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>200</v>
+        <v>-25</v>
       </c>
       <c r="F23" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H23" s="15">
-        <v>10</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I23" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J23" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K23" s="15">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L23" s="15">
-        <v>-13.333333333333</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="M23" s="15">
-        <v>85.714285714285</v>
+        <v>76.470588235294</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-23.529411764705</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F24" s="14">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G24" s="14">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H24" s="15">
-        <v>-11.764705882352</v>
+        <v>-14.925373134328</v>
       </c>
       <c r="I24" s="14">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="J24" s="14">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="K24" s="15">
-        <v>0</v>
+        <v>-2.739726027397</v>
       </c>
       <c r="L24" s="15">
-        <v>-19.108280254777</v>
+        <v>-19.318181818181</v>
       </c>
       <c r="M24" s="15">
-        <v>-15.894039735099</v>
+        <v>-11.801242236024</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
         <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="14">
+        <v>13</v>
+      </c>
+      <c r="G25" s="14">
         <v>15</v>
       </c>
-      <c r="G25" s="14">
-        <v>19</v>
-      </c>
       <c r="H25" s="15">
-        <v>-21.052631578947</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J25" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K25" s="15">
-        <v>-11.428571428571</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="L25" s="15">
-        <v>-34.042553191489</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>10</v>
+      </c>
+      <c r="D26" s="14">
         <v>12</v>
       </c>
-      <c r="D26" s="14">
-        <v>8</v>
-      </c>
       <c r="E26" s="15">
-        <v>50</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>13.953488372093</v>
+        <v>4.761904761904</v>
       </c>
       <c r="I26" s="14">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="J26" s="14">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="K26" s="15">
-        <v>-10</v>
+        <v>-11.607142857142</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.094339622641</v>
+        <v>-20.8</v>
       </c>
       <c r="M26" s="15">
-        <v>60.714285714285</v>
+        <v>45.588235294117</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>-71.428571428571</v>
+        <v>-62.5</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>-55.555555555555</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>-11.111111111111</v>
+        <v>-25</v>
       </c>
       <c r="L28" s="15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,39 +1541,39 @@
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="14">
+        <v>2</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I31" s="14">
         <v>1</v>
       </c>
-      <c r="H31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-060pct.xlsx
+++ b/data/source/weekly/cs-en-us-060pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,23 +869,23 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -901,23 +901,23 @@
       <c r="E15" s="15">
         <v>-100</v>
       </c>
-      <c r="F15" s="14">
-        <v>2</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
         <v>7</v>
       </c>
       <c r="H15" s="15">
-        <v>-71.428571428571</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L15" s="15">
         <v>100</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="E16" s="15">
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
         <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
+        <v>24</v>
+      </c>
+      <c r="J16" s="14">
         <v>22</v>
       </c>
-      <c r="J16" s="14">
-        <v>20</v>
-      </c>
       <c r="K16" s="15">
-        <v>10</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.666666666666</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="M16" s="15">
         <v>-50</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.601036269430</v>
+        <v>-88.837209302325</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-57.142857142857</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F17" s="14">
         <v>32</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H17" s="15">
-        <v>18.518518518518</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I17" s="14">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J17" s="14">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="K17" s="15">
-        <v>54.716981132075</v>
+        <v>40.625</v>
       </c>
       <c r="L17" s="15">
-        <v>26.153846153846</v>
+        <v>25</v>
       </c>
       <c r="M17" s="15">
-        <v>290.47619047619</v>
+        <v>291.304347826087</v>
       </c>
       <c r="N17" s="15">
-        <v>-32.231404958677</v>
+        <v>-32.835820895522</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J18" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K18" s="15">
-        <v>-13.043478260869</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="L18" s="15">
-        <v>33.333333333333</v>
+        <v>35.294117647058</v>
       </c>
       <c r="M18" s="15">
-        <v>-9.090909090909</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.247311827957</v>
+        <v>-89.150943396226</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H19" s="15">
-        <v>68.421052631578</v>
+        <v>43.478260869565</v>
       </c>
       <c r="I19" s="14">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J19" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K19" s="15">
-        <v>18.367346938775</v>
+        <v>16.363636363636</v>
       </c>
       <c r="L19" s="15">
-        <v>-1.694915254237</v>
+        <v>1.587301587301</v>
       </c>
       <c r="M19" s="15">
-        <v>-28.395061728395</v>
+        <v>-28.888888888888</v>
       </c>
       <c r="N19" s="15">
-        <v>-40.206185567010</v>
+        <v>-39.622641509434</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
         <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J20" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K20" s="15">
-        <v>20</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L20" s="15">
-        <v>-36.842105263157</v>
+        <v>-25</v>
       </c>
       <c r="M20" s="15">
-        <v>-45.454545454545</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.548387096774</v>
+        <v>-92.574257425742</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>-26.923076923076</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G21" s="17">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="H21" s="18">
-        <v>17.333333333333</v>
+        <v>4.597701149425</v>
       </c>
       <c r="I21" s="17">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="J21" s="17">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="K21" s="18">
-        <v>19.277108433734</v>
+        <v>13.917525773195</v>
       </c>
       <c r="L21" s="18">
-        <v>3.664921465968</v>
+        <v>5.741626794258</v>
       </c>
       <c r="M21" s="18">
-        <v>3.664921465968</v>
+        <v>3.755868544600</v>
       </c>
       <c r="N21" s="18">
-        <v>-75</v>
+        <v>-74.857792946530</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>5</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>400</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>7</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>250</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>9</v>
       </c>
       <c r="J22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="L22" s="15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
         <v>3</v>
       </c>
-      <c r="D23" s="14">
-        <v>4</v>
-      </c>
       <c r="E23" s="15">
-        <v>-25</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23" s="14">
         <v>13</v>
       </c>
       <c r="H23" s="15">
-        <v>-7.692307692307</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I23" s="14">
         <v>30</v>
       </c>
       <c r="J23" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K23" s="15">
-        <v>25</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L23" s="15">
-        <v>-11.764705882352</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="M23" s="15">
-        <v>76.470588235294</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>-15.789473684210</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F24" s="14">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G24" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H24" s="15">
-        <v>-14.925373134328</v>
+        <v>-29.577464788732</v>
       </c>
       <c r="I24" s="14">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J24" s="14">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.739726027397</v>
+        <v>-5.521472392638</v>
       </c>
       <c r="L24" s="15">
-        <v>-19.318181818181</v>
+        <v>-19.371727748691</v>
       </c>
       <c r="M24" s="15">
-        <v>-11.801242236024</v>
+        <v>-14.917127071823</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
         <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G25" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H25" s="15">
-        <v>-13.333333333333</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I25" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J25" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K25" s="15">
-        <v>-12.820512820512</v>
+        <v>-16.279069767441</v>
       </c>
       <c r="L25" s="15">
-        <v>-33.333333333333</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-16.666666666666</v>
+        <v>63.636363636363</v>
       </c>
       <c r="F26" s="14">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G26" s="14">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H26" s="15">
-        <v>4.761904761904</v>
+        <v>27.5</v>
       </c>
       <c r="I26" s="14">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="J26" s="14">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.607142857142</v>
+        <v>-4.878048780487</v>
       </c>
       <c r="L26" s="15">
-        <v>-20.8</v>
+        <v>-13.970588235294</v>
       </c>
       <c r="M26" s="15">
-        <v>45.588235294117</v>
+        <v>46.25</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F27" s="14">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>-62.5</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>-54.545454545454</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="L27" s="15">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>3</v>
       </c>
-      <c r="E28" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F28" s="14">
-        <v>2</v>
-      </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-66.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
         <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>-25</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>80</v>
+        <v>37.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.888888888888</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,45 +1526,45 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.888888888888</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
-      </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>0</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-060pct.xlsx
+++ b/data/source/weekly/cs-en-us-060pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-75</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,17 +895,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
         <v>-100</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I16" s="14">
+        <v>25</v>
+      </c>
+      <c r="J16" s="14">
         <v>24</v>
       </c>
-      <c r="J16" s="14">
-        <v>22</v>
-      </c>
       <c r="K16" s="15">
-        <v>9.090909090909</v>
+        <v>4.166666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-29.411764705882</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-55.357142857142</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.837209302325</v>
+        <v>-89.539748953974</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-27.272727272727</v>
+        <v>550</v>
       </c>
       <c r="F17" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G17" s="14">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H17" s="15">
-        <v>-5.882352941176</v>
+        <v>26.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="J17" s="14">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K17" s="15">
-        <v>40.625</v>
+        <v>56.060606060606</v>
       </c>
       <c r="L17" s="15">
-        <v>25</v>
+        <v>35.526315789473</v>
       </c>
       <c r="M17" s="15">
-        <v>291.304347826087</v>
+        <v>267.857142857143</v>
       </c>
       <c r="N17" s="15">
-        <v>-32.835820895522</v>
+        <v>-32.236842105263</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
         <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J18" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K18" s="15">
-        <v>-14.814814814814</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="L18" s="15">
-        <v>35.294117647058</v>
+        <v>25</v>
       </c>
       <c r="M18" s="15">
-        <v>-17.857142857142</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.150943396226</v>
+        <v>-89.082969432314</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
         <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G19" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H19" s="15">
-        <v>43.478260869565</v>
+        <v>30</v>
       </c>
       <c r="I19" s="14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J19" s="14">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K19" s="15">
-        <v>16.363636363636</v>
+        <v>14.035087719298</v>
       </c>
       <c r="L19" s="15">
-        <v>1.587301587301</v>
+        <v>-4.411764705882</v>
       </c>
       <c r="M19" s="15">
-        <v>-28.888888888888</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="N19" s="15">
-        <v>-39.622641509434</v>
+        <v>-44.444444444444</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I20" s="14">
         <v>15</v>
       </c>
       <c r="J20" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K20" s="15">
-        <v>15.384615384615</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L20" s="15">
         <v>-25</v>
       </c>
       <c r="M20" s="15">
-        <v>-34.782608695652</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.574257425742</v>
+        <v>-93.119266055045</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.857142857142</v>
+        <v>72.727272727272</v>
       </c>
       <c r="F21" s="17">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G21" s="17">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H21" s="18">
-        <v>4.597701149425</v>
+        <v>8.75</v>
       </c>
       <c r="I21" s="17">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="J21" s="17">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="K21" s="18">
-        <v>13.917525773195</v>
+        <v>16.097560975609</v>
       </c>
       <c r="L21" s="18">
-        <v>5.741626794258</v>
+        <v>6.25</v>
       </c>
       <c r="M21" s="18">
-        <v>3.755868544600</v>
+        <v>1.276595744680</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.857792946530</v>
+        <v>-75.413223140495</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>133.333333333333</v>
+        <v>300</v>
       </c>
       <c r="I22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
         <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,23 +1220,23 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="14">
-        <v>3</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-66.666666666666</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G23" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>-15.384615384615</v>
+        <v>-12.5</v>
       </c>
       <c r="I23" s="14">
         <v>30</v>
@@ -1248,7 +1248,7 @@
         <v>11.111111111111</v>
       </c>
       <c r="L23" s="15">
-        <v>-21.052631578947</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M23" s="15">
         <v>66.666666666666</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E24" s="15">
-        <v>-29.411764705882</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="F24" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G24" s="14">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="H24" s="15">
-        <v>-29.577464788732</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="I24" s="14">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="J24" s="14">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="K24" s="15">
-        <v>-5.521472392638</v>
+        <v>-9.895833333333</v>
       </c>
       <c r="L24" s="15">
-        <v>-19.371727748691</v>
+        <v>-18.396226415094</v>
       </c>
       <c r="M24" s="15">
-        <v>-14.917127071823</v>
+        <v>-13.5</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F25" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G25" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H25" s="15">
-        <v>-35.714285714285</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="I25" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J25" s="14">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="K25" s="15">
-        <v>-16.279069767441</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L25" s="15">
-        <v>-36.842105263157</v>
+        <v>-34.426229508196</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>15</v>
+      </c>
+      <c r="D26" s="14">
         <v>18</v>
       </c>
-      <c r="D26" s="14">
-        <v>11</v>
-      </c>
       <c r="E26" s="15">
-        <v>63.636363636363</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G26" s="14">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H26" s="15">
-        <v>27.5</v>
+        <v>12.244897959183</v>
       </c>
       <c r="I26" s="14">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="J26" s="14">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.878048780487</v>
+        <v>-6.382978723404</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.970588235294</v>
+        <v>-11.409395973154</v>
       </c>
       <c r="M26" s="15">
-        <v>46.25</v>
+        <v>51.724137931034</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
         <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>-69.230769230769</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
         <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>-8.333333333333</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="L28" s="15">
         <v>37.5</v>
@@ -1466,17 +1466,17 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
         <v>1</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="14">
-        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1500,24 +1500,24 @@
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-80</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="14">
-        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1541,15 +1541,15 @@
         <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-80</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,22 +1558,22 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="14">
         <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-060pct.xlsx
+++ b/data/source/weekly/cs-en-us-060pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -885,15 +885,15 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,32 +901,32 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>-66.666666666666</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
         <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>28.571428571428</v>
+        <v>50</v>
       </c>
       <c r="I16" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J16" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>4.166666666666</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L16" s="15">
-        <v>-32.432432432432</v>
+        <v>-28.205128205128</v>
       </c>
       <c r="M16" s="15">
-        <v>-55.357142857142</v>
+        <v>-54.838709677419</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.539748953974</v>
+        <v>-89.019607843137</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>550</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H17" s="15">
-        <v>26.666666666666</v>
+        <v>11.428571428571</v>
       </c>
       <c r="I17" s="14">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="J17" s="14">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K17" s="15">
-        <v>56.060606060606</v>
+        <v>55.405405405405</v>
       </c>
       <c r="L17" s="15">
-        <v>35.526315789473</v>
+        <v>43.75</v>
       </c>
       <c r="M17" s="15">
-        <v>267.857142857143</v>
+        <v>296.551724137931</v>
       </c>
       <c r="N17" s="15">
-        <v>-32.236842105263</v>
+        <v>-29.447852760736</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
+        <v>8</v>
+      </c>
+      <c r="G18" s="14">
         <v>9</v>
       </c>
-      <c r="G18" s="14">
-        <v>8</v>
-      </c>
       <c r="H18" s="15">
-        <v>12.5</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I18" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>-10.714285714285</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="L18" s="15">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M18" s="15">
-        <v>-13.793103448275</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.082969432314</v>
+        <v>-89.430894308943</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>2</v>
       </c>
       <c r="D19" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G19" s="14">
         <v>20</v>
       </c>
       <c r="H19" s="15">
-        <v>30</v>
+        <v>-10</v>
       </c>
       <c r="I19" s="14">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J19" s="14">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K19" s="15">
-        <v>14.035087719298</v>
+        <v>9.836065573770</v>
       </c>
       <c r="L19" s="15">
-        <v>-4.411764705882</v>
+        <v>-8.219178082191</v>
       </c>
       <c r="M19" s="15">
-        <v>-31.578947368421</v>
+        <v>-36.792452830188</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.444444444444</v>
+        <v>-45.528455284552</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>4</v>
-      </c>
       <c r="E20" s="15">
-        <v>-75</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
         <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>-55.555555555555</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J20" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K20" s="15">
-        <v>-11.764705882352</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-25</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M20" s="15">
-        <v>-42.307692307692</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.119266055045</v>
+        <v>-92.561983471074</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>72.727272727272</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F21" s="17">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G21" s="17">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H21" s="18">
-        <v>8.75</v>
+        <v>-1.204819277108</v>
       </c>
       <c r="I21" s="17">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="J21" s="17">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="K21" s="18">
-        <v>16.097560975609</v>
+        <v>16.591928251121</v>
       </c>
       <c r="L21" s="18">
-        <v>6.25</v>
+        <v>9.243697478991</v>
       </c>
       <c r="M21" s="18">
-        <v>1.276595744680</v>
+        <v>1.167315175097</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.413223140495</v>
+        <v>-75.071907957814</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13" t="s">
+      <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L22" s="15">
         <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23" s="15">
-        <v>-12.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J23" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K23" s="15">
-        <v>11.111111111111</v>
+        <v>10.344827586206</v>
       </c>
       <c r="L23" s="15">
-        <v>-23.076923076923</v>
+        <v>-20</v>
       </c>
       <c r="M23" s="15">
-        <v>66.666666666666</v>
+        <v>77.777777777777</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>-34.482758620689</v>
+        <v>5</v>
       </c>
       <c r="F24" s="14">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G24" s="14">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H24" s="15">
-        <v>-26.829268292682</v>
+        <v>-20</v>
       </c>
       <c r="I24" s="14">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="J24" s="14">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.895833333333</v>
+        <v>-8.490566037735</v>
       </c>
       <c r="L24" s="15">
-        <v>-18.396226415094</v>
+        <v>-18.828451882845</v>
       </c>
       <c r="M24" s="15">
-        <v>-13.5</v>
+        <v>-8.920187793427</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-55.555555555555</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H25" s="15">
-        <v>-47.619047619047</v>
+        <v>-30</v>
       </c>
       <c r="I25" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J25" s="14">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K25" s="15">
-        <v>-23.076923076923</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L25" s="15">
-        <v>-34.426229508196</v>
+        <v>-32.835820895522</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>16</v>
+      </c>
+      <c r="D26" s="14">
         <v>15</v>
       </c>
-      <c r="D26" s="14">
-        <v>18</v>
-      </c>
       <c r="E26" s="15">
-        <v>-16.666666666666</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G26" s="14">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H26" s="15">
-        <v>12.244897959183</v>
+        <v>5.357142857142</v>
       </c>
       <c r="I26" s="14">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="J26" s="14">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.382978723404</v>
+        <v>-5.128205128205</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.409395973154</v>
+        <v>-7.5</v>
       </c>
       <c r="M26" s="15">
-        <v>51.724137931034</v>
+        <v>49.494949494949</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I27" s="14">
         <v>6</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-83.333333333333</v>
-      </c>
-      <c r="I27" s="14">
-        <v>5</v>
       </c>
       <c r="J27" s="14">
         <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>-61.538461538461</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="L27" s="15">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,7 +1429,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
@@ -1438,22 +1438,22 @@
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
       <c r="I28" s="14">
         <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>-21.428571428571</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="L28" s="15">
-        <v>37.5</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.235294117647</v>
+        <v>-78.947368421052</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,54 +1526,54 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N30" s="15">
-        <v>-85.714285714285</v>
+        <v>-81.25</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
-      </c>
-      <c r="D31" s="13" t="s">
+      <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>4</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>2</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H31" s="15">
-        <v>100</v>
+        <v>-60</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
       </c>
       <c r="J31" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-060pct.xlsx
+++ b/data/source/weekly/cs-en-us-060pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,10 +905,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>5</v>
@@ -920,7 +920,7 @@
         <v>-58.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>4</v>
+      </c>
+      <c r="D16" s="14">
         <v>3</v>
       </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
+        <v>11</v>
+      </c>
+      <c r="G16" s="14">
         <v>9</v>
       </c>
-      <c r="G16" s="14">
-        <v>6</v>
-      </c>
       <c r="H16" s="15">
-        <v>50</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I16" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J16" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K16" s="15">
-        <v>7.692307692307</v>
+        <v>10.344827586206</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.205128205128</v>
+        <v>-20</v>
       </c>
       <c r="M16" s="15">
-        <v>-54.838709677419</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.019607843137</v>
+        <v>-88.571428571428</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F17" s="14">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G17" s="14">
         <v>35</v>
       </c>
       <c r="H17" s="15">
-        <v>11.428571428571</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J17" s="14">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="K17" s="15">
-        <v>55.405405405405</v>
+        <v>32.954545454545</v>
       </c>
       <c r="L17" s="15">
-        <v>43.75</v>
+        <v>40.963855421686</v>
       </c>
       <c r="M17" s="15">
-        <v>296.551724137931</v>
+        <v>265.625</v>
       </c>
       <c r="N17" s="15">
-        <v>-29.447852760736</v>
+        <v>-36.756756756756</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="14">
         <v>3</v>
       </c>
-      <c r="E18" s="15">
-        <v>-66.666666666666</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
         <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
         <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.129032258064</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="L18" s="15">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M18" s="15">
-        <v>-16.129032258064</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.430894308943</v>
+        <v>-89.416058394160</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
         <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G19" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H19" s="15">
-        <v>-10</v>
+        <v>-18.75</v>
       </c>
       <c r="I19" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J19" s="14">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K19" s="15">
-        <v>9.836065573770</v>
+        <v>9.230769230769</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.219178082191</v>
+        <v>-7.792207792207</v>
       </c>
       <c r="M19" s="15">
-        <v>-36.792452830188</v>
+        <v>-35.454545454545</v>
       </c>
       <c r="N19" s="15">
-        <v>-45.528455284552</v>
+        <v>-48.550724637681</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I20" s="14">
         <v>18</v>
       </c>
       <c r="J20" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>-18.181818181818</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="M20" s="15">
-        <v>-35.714285714285</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.561983471074</v>
+        <v>-93.181818181818</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>22.222222222222</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G21" s="17">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.204819277108</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="I21" s="17">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="J21" s="17">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="K21" s="18">
-        <v>16.591928251121</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L21" s="18">
-        <v>9.243697478991</v>
+        <v>10.080645161290</v>
       </c>
       <c r="M21" s="18">
-        <v>1.167315175097</v>
+        <v>-0.364963503649</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.071907957814</v>
+        <v>-76.363636363636</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>2</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>6</v>
-      </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22" s="14">
         <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>42.857142857142</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L22" s="15">
-        <v>66.666666666666</v>
+        <v>83.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>-33.333333333333</v>
+        <v>-37.5</v>
       </c>
       <c r="I23" s="14">
+        <v>34</v>
+      </c>
+      <c r="J23" s="14">
         <v>32</v>
       </c>
-      <c r="J23" s="14">
-        <v>29</v>
-      </c>
       <c r="K23" s="15">
-        <v>10.344827586206</v>
+        <v>6.25</v>
       </c>
       <c r="L23" s="15">
-        <v>-20</v>
+        <v>-17.073170731707</v>
       </c>
       <c r="M23" s="15">
-        <v>77.777777777777</v>
+        <v>61.904761904761</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>5</v>
+        <v>58.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G24" s="14">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H24" s="15">
-        <v>-20</v>
+        <v>-8.974358974358</v>
       </c>
       <c r="I24" s="14">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="J24" s="14">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="K24" s="15">
-        <v>-8.490566037735</v>
+        <v>-4.910714285714</v>
       </c>
       <c r="L24" s="15">
-        <v>-18.828451882845</v>
+        <v>-15.810276679841</v>
       </c>
       <c r="M24" s="15">
-        <v>-8.920187793427</v>
+        <v>-6.986899563318</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1312,25 +1312,25 @@
         <v>66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H25" s="15">
-        <v>-30</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="I25" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J25" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K25" s="15">
-        <v>-18.181818181818</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="L25" s="15">
-        <v>-32.835820895522</v>
+        <v>-25.373134328358</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>6.666666666666</v>
+        <v>27.272727272727</v>
       </c>
       <c r="F26" s="14">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G26" s="14">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H26" s="15">
-        <v>5.357142857142</v>
+        <v>14.545454545454</v>
       </c>
       <c r="I26" s="14">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="J26" s="14">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.128205128205</v>
+        <v>-2.994011976047</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.5</v>
+        <v>-5.813953488372</v>
       </c>
       <c r="M26" s="15">
-        <v>49.494949494949</v>
+        <v>54.285714285714</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,10 +1397,10 @@
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>6</v>
@@ -1412,7 +1412,7 @@
         <v>-53.846153846153</v>
       </c>
       <c r="L27" s="15">
-        <v>-14.285714285714</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>-62.5</v>
+        <v>-75</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>-35.294117647058</v>
+        <v>-40</v>
       </c>
       <c r="L28" s="15">
-        <v>22.222222222222</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1497,18 +1497,18 @@
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-78.947368421052</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1538,42 +1538,42 @@
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-81.25</v>
+        <v>-82.352941176470</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="14">
-        <v>4</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>2</v>
       </c>
       <c r="G31" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H31" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="14">
         <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-060pct.xlsx
+++ b/data/source/weekly/cs-en-us-060pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="14">
+      <c r="G14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L14" s="15">
         <v>0</v>
@@ -890,43 +890,43 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-50</v>
+      </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>-58.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L15" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N15" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>22.222222222222</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J16" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K16" s="15">
-        <v>10.344827586206</v>
+        <v>8.823529411764</v>
       </c>
       <c r="L16" s="15">
-        <v>-20</v>
+        <v>-11.904761904761</v>
       </c>
       <c r="M16" s="15">
-        <v>-52.941176470588</v>
+        <v>-47.142857142857</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.571428571428</v>
+        <v>-87.414965986394</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-85.714285714285</v>
+        <v>116.666666666667</v>
       </c>
       <c r="F17" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G17" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I17" s="14">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="J17" s="14">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K17" s="15">
-        <v>32.954545454545</v>
+        <v>37.234042553191</v>
       </c>
       <c r="L17" s="15">
-        <v>40.963855421686</v>
+        <v>44.943820224719</v>
       </c>
       <c r="M17" s="15">
-        <v>265.625</v>
+        <v>279.411764705882</v>
       </c>
       <c r="N17" s="15">
-        <v>-36.756756756756</v>
+        <v>-34.183673469387</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,34 +1022,34 @@
         <v>20</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I18" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J18" s="14">
         <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>-6.451612903225</v>
+        <v>6.451612903225</v>
       </c>
       <c r="L18" s="15">
-        <v>45</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M18" s="15">
-        <v>-14.705882352941</v>
+        <v>-10.810810810810</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.416058394160</v>
+        <v>-88.581314878892</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F19" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H19" s="15">
-        <v>-18.75</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="J19" s="14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K19" s="15">
-        <v>9.230769230769</v>
+        <v>18.571428571428</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.792207792207</v>
+        <v>-3.488372093023</v>
       </c>
       <c r="M19" s="15">
-        <v>-35.454545454545</v>
+        <v>-30.833333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.550724637681</v>
+        <v>-45.033112582781</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F20" s="14">
         <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>-45.454545454545</v>
+        <v>-60</v>
       </c>
       <c r="I20" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J20" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K20" s="15">
-        <v>-14.285714285714</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L20" s="15">
-        <v>-21.739130434782</v>
+        <v>-20</v>
       </c>
       <c r="M20" s="15">
-        <v>-37.931034482758</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.181818181818</v>
+        <v>-93.127147766323</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>-45.833333333333</v>
+        <v>34.615384615384</v>
       </c>
       <c r="F21" s="17">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G21" s="17">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.407407407407</v>
+        <v>13.924050632911</v>
       </c>
       <c r="I21" s="17">
+        <v>309</v>
+      </c>
+      <c r="J21" s="17">
         <v>273</v>
       </c>
-      <c r="J21" s="17">
-        <v>247</v>
-      </c>
       <c r="K21" s="18">
-        <v>10.526315789473</v>
+        <v>13.186813186813</v>
       </c>
       <c r="L21" s="18">
-        <v>10.080645161290</v>
+        <v>15.298507462686</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.364963503649</v>
+        <v>5.460750853242</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.363636363636</v>
+        <v>-74.979757085020</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1186,34 +1186,34 @@
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="14">
+        <v>3</v>
+      </c>
+      <c r="G22" s="14">
         <v>2</v>
       </c>
-      <c r="G22" s="14">
-        <v>3</v>
-      </c>
       <c r="H22" s="15">
-        <v>-33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I22" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J22" s="14">
         <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>57.142857142857</v>
+        <v>71.428571428571</v>
       </c>
       <c r="L22" s="15">
-        <v>83.333333333333</v>
+        <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D23" s="14">
         <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
         <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>-37.5</v>
+        <v>12.5</v>
       </c>
       <c r="I23" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J23" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K23" s="15">
-        <v>6.25</v>
+        <v>11.428571428571</v>
       </c>
       <c r="L23" s="15">
-        <v>-17.073170731707</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="M23" s="15">
-        <v>61.904761904761</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>58.333333333333</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="F24" s="14">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G24" s="14">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.974358974358</v>
+        <v>-9.756097560975</v>
       </c>
       <c r="I24" s="14">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="J24" s="14">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="K24" s="15">
-        <v>-4.910714285714</v>
+        <v>-6.938775510204</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.810276679841</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M24" s="15">
-        <v>-6.986899563318</v>
+        <v>-8.064516129032</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>66.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="F25" s="14">
         <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H25" s="15">
-        <v>-15.789473684210</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="I25" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J25" s="14">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="K25" s="15">
-        <v>-13.793103448275</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="L25" s="15">
-        <v>-25.373134328358</v>
+        <v>-26.760563380281</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,81 +1344,81 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>27.272727272727</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="F26" s="14">
+        <v>56</v>
+      </c>
+      <c r="G26" s="14">
         <v>63</v>
       </c>
-      <c r="G26" s="14">
-        <v>55</v>
-      </c>
       <c r="H26" s="15">
-        <v>14.545454545454</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I26" s="14">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="J26" s="14">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.994011976047</v>
+        <v>-6.989247311827</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.813953488372</v>
+        <v>-8.465608465608</v>
       </c>
       <c r="M26" s="15">
-        <v>54.285714285714</v>
+        <v>53.097345132743</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>-53.846153846153</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1428,11 +1428,11 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-66.666666666666</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
@@ -1444,118 +1444,118 @@
         <v>-75</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
         <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>-40</v>
+        <v>-35</v>
       </c>
       <c r="L28" s="15">
-        <v>33.333333333333</v>
+        <v>30</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
       </c>
       <c r="F29" s="14">
         <v>3</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>200</v>
       </c>
       <c r="I29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L29" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M29" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-80</v>
+        <v>-77.272727272727</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>100</v>
       </c>
       <c r="I30" s="14">
+        <v>4</v>
+      </c>
+      <c r="J30" s="14">
         <v>3</v>
       </c>
-      <c r="J30" s="14">
-        <v>2</v>
-      </c>
       <c r="K30" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-82.352941176470</v>
+        <v>-78.947368421052</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="14">
         <v>2</v>
@@ -1576,13 +1576,13 @@
         <v>-50</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>52</v>

--- a/data/source/weekly/cs-en-us-060pct.xlsx
+++ b/data/source/weekly/cs-en-us-060pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,40 +890,40 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
         <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K15" s="15">
-        <v>-57.142857142857</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N15" s="15">
         <v>0</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
-      </c>
-      <c r="D16" s="14">
-        <v>5</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
         <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>8.333333333333</v>
+        <v>30</v>
       </c>
       <c r="I16" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J16" s="14">
         <v>34</v>
       </c>
       <c r="K16" s="15">
-        <v>8.823529411764</v>
+        <v>11.764705882352</v>
       </c>
       <c r="L16" s="15">
-        <v>-11.904761904761</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.142857142857</v>
+        <v>-49.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.414965986394</v>
+        <v>-87.458745874587</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
         <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>116.666666666667</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G17" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H17" s="15">
-        <v>30</v>
+        <v>2.941176470588</v>
       </c>
       <c r="I17" s="14">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J17" s="14">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="K17" s="15">
-        <v>37.234042553191</v>
+        <v>38</v>
       </c>
       <c r="L17" s="15">
-        <v>44.943820224719</v>
+        <v>40.816326530612</v>
       </c>
       <c r="M17" s="15">
-        <v>279.411764705882</v>
+        <v>245</v>
       </c>
       <c r="N17" s="15">
-        <v>-34.183673469387</v>
+        <v>-35.813953488372</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>3</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>22</v>
+      <c r="E18" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I18" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J18" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K18" s="15">
-        <v>6.451612903225</v>
+        <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>57.142857142857</v>
+        <v>54.545454545454</v>
       </c>
       <c r="M18" s="15">
-        <v>-10.810810810810</v>
+        <v>-15</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.581314878892</v>
+        <v>-88.925081433224</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
         <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G19" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H19" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I19" s="14">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J19" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K19" s="15">
-        <v>18.571428571428</v>
+        <v>22.666666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.488372093023</v>
+        <v>-3.157894736842</v>
       </c>
       <c r="M19" s="15">
-        <v>-30.833333333333</v>
+        <v>-28.125</v>
       </c>
       <c r="N19" s="15">
-        <v>-45.033112582781</v>
+        <v>-43.209876543209</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="14">
-        <v>7</v>
-      </c>
       <c r="E20" s="15">
-        <v>-71.428571428571</v>
+        <v>50</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>-60</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I20" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J20" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K20" s="15">
-        <v>-28.571428571428</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-20</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="M20" s="15">
-        <v>-35.483870967741</v>
+        <v>-28.125</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.127147766323</v>
+        <v>-92.987804878048</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>34.615384615384</v>
+        <v>41.176470588235</v>
       </c>
       <c r="F21" s="17">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H21" s="18">
-        <v>13.924050632911</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I21" s="17">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="J21" s="17">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="K21" s="18">
-        <v>13.186813186813</v>
+        <v>14.827586206896</v>
       </c>
       <c r="L21" s="18">
-        <v>15.298507462686</v>
+        <v>14.432989690721</v>
       </c>
       <c r="M21" s="18">
-        <v>5.460750853242</v>
+        <v>5.379746835443</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.979757085020</v>
+        <v>-74.962406015037</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,38 +1182,38 @@
       <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>22</v>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="I22" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J22" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K22" s="15">
-        <v>71.428571428571</v>
+        <v>44.444444444444</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>116.666666666667</v>
       </c>
       <c r="M22" s="15">
-        <v>-7.692307692307</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>5</v>
-      </c>
-      <c r="D23" s="14">
         <v>3</v>
       </c>
-      <c r="E23" s="15">
-        <v>66.666666666666</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
         <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J23" s="14">
         <v>35</v>
       </c>
       <c r="K23" s="15">
-        <v>11.428571428571</v>
+        <v>20</v>
       </c>
       <c r="L23" s="15">
-        <v>-9.302325581395</v>
+        <v>-10.638297872340</v>
       </c>
       <c r="M23" s="15">
-        <v>85.714285714285</v>
+        <v>90.909090909090</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>-23.809523809523</v>
+        <v>4.347826086956</v>
       </c>
       <c r="F24" s="14">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.756097560975</v>
+        <v>3.947368421052</v>
       </c>
       <c r="I24" s="14">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="J24" s="14">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.938775510204</v>
+        <v>-5.970149253731</v>
       </c>
       <c r="L24" s="15">
-        <v>-13.636363636363</v>
+        <v>-9.352517985611</v>
       </c>
       <c r="M24" s="15">
-        <v>-8.064516129032</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-62.5</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
         <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H25" s="15">
-        <v>-30.434782608695</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I25" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J25" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K25" s="15">
-        <v>-21.212121212121</v>
+        <v>-20</v>
       </c>
       <c r="L25" s="15">
-        <v>-26.760563380281</v>
+        <v>-25.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>9</v>
+      </c>
+      <c r="D26" s="14">
         <v>11</v>
       </c>
-      <c r="D26" s="14">
-        <v>19</v>
-      </c>
       <c r="E26" s="15">
-        <v>-42.105263157894</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F26" s="14">
+        <v>50</v>
+      </c>
+      <c r="G26" s="14">
         <v>56</v>
       </c>
-      <c r="G26" s="14">
-        <v>63</v>
-      </c>
       <c r="H26" s="15">
-        <v>-11.111111111111</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="I26" s="14">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="J26" s="14">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.989247311827</v>
+        <v>-7.614213197969</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.465608465608</v>
+        <v>-9.900990099009</v>
       </c>
       <c r="M26" s="15">
-        <v>53.097345132743</v>
+        <v>52.941176470588</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1388,78 +1388,78 @@
         <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K27" s="15">
-        <v>-53.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
         <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>-35</v>
+        <v>-40</v>
       </c>
       <c r="L28" s="15">
-        <v>30</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,38 +1469,38 @@
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I29" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29" s="14">
         <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>66.666666666666</v>
-      </c>
-      <c r="L29" s="13" t="s">
-        <v>22</v>
+        <v>100</v>
+      </c>
+      <c r="L29" s="15">
+        <v>500</v>
       </c>
       <c r="M29" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="N29" s="15">
-        <v>-77.272727272727</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="14">
         <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>33.333333333333</v>
-      </c>
-      <c r="L30" s="13" t="s">
-        <v>22</v>
+        <v>66.666666666666</v>
+      </c>
+      <c r="L30" s="15">
+        <v>400</v>
       </c>
       <c r="M30" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-78.947368421052</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,38 +1551,38 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>22</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" s="15">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
       </c>
       <c r="J31" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K31" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="L33" s="15">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>52</v>

--- a/data/source/weekly/cs-en-us-060pct.xlsx
+++ b/data/source/weekly/cs-en-us-060pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -905,28 +905,28 @@
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K15" s="15">
-        <v>-53.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,7 +934,7 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -946,28 +946,28 @@
         <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>30</v>
+        <v>62.5</v>
       </c>
       <c r="I16" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J16" s="14">
         <v>34</v>
       </c>
       <c r="K16" s="15">
-        <v>11.764705882352</v>
+        <v>20.588235294117</v>
       </c>
       <c r="L16" s="15">
-        <v>-13.636363636363</v>
+        <v>-12.765957446808</v>
       </c>
       <c r="M16" s="15">
-        <v>-49.333333333333</v>
+        <v>-48.101265822784</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.458745874587</v>
+        <v>-87.066246056782</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G17" s="14">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H17" s="15">
-        <v>2.941176470588</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="I17" s="14">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="J17" s="14">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="K17" s="15">
-        <v>38</v>
+        <v>27.826086956521</v>
       </c>
       <c r="L17" s="15">
-        <v>40.816326530612</v>
+        <v>34.862385321100</v>
       </c>
       <c r="M17" s="15">
-        <v>245</v>
+        <v>234.090909090909</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.813953488372</v>
+        <v>-35.807860262008</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>50</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I18" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J18" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>-2.631578947368</v>
       </c>
       <c r="L18" s="15">
-        <v>54.545454545454</v>
+        <v>54.166666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-15</v>
+        <v>-11.904761904761</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.925081433224</v>
+        <v>-88.615384615384</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>80</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F19" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G19" s="14">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="I19" s="14">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="J19" s="14">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K19" s="15">
-        <v>22.666666666666</v>
+        <v>15.116279069767</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.157894736842</v>
+        <v>-7.476635514018</v>
       </c>
       <c r="M19" s="15">
-        <v>-28.125</v>
+        <v>-25.563909774436</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.209876543209</v>
+        <v>-41.764705882352</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
-      </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
-      <c r="E20" s="15">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>-38.461538461538</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J20" s="14">
         <v>30</v>
       </c>
       <c r="K20" s="15">
-        <v>-23.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="L20" s="15">
-        <v>-14.814814814814</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="M20" s="15">
-        <v>-28.125</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.987804878048</v>
+        <v>-93.162393162393</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,51 +1142,51 @@
         <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E21" s="18">
-        <v>41.176470588235</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="F21" s="17">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G21" s="17">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="H21" s="18">
-        <v>11.764705882352</v>
+        <v>-1.020408163265</v>
       </c>
       <c r="I21" s="17">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="J21" s="17">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="K21" s="18">
-        <v>14.827586206896</v>
+        <v>11.214953271028</v>
       </c>
       <c r="L21" s="18">
-        <v>14.432989690721</v>
+        <v>10.526315789473</v>
       </c>
       <c r="M21" s="18">
-        <v>5.379746835443</v>
+        <v>7.530120481927</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.962406015037</v>
+        <v>-74.644886363636</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
         <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
@@ -1201,16 +1201,16 @@
         <v>13</v>
       </c>
       <c r="J22" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>44.444444444444</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L22" s="15">
-        <v>116.666666666667</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M22" s="15">
-        <v>-7.142857142857</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
+        <v>5</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-60</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I23" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J23" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K23" s="15">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="L23" s="15">
-        <v>-10.638297872340</v>
+        <v>-10</v>
       </c>
       <c r="M23" s="15">
-        <v>90.909090909090</v>
+        <v>87.5</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>4.347826086956</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F24" s="14">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G24" s="14">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H24" s="15">
-        <v>3.947368421052</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="J24" s="14">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="K24" s="15">
-        <v>-5.970149253731</v>
+        <v>-6.293706293706</v>
       </c>
       <c r="L24" s="15">
-        <v>-9.352517985611</v>
+        <v>-8.219178082191</v>
       </c>
       <c r="M24" s="15">
-        <v>-8.695652173913</v>
+        <v>-12.131147540983</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="F25" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H25" s="15">
-        <v>-11.111111111111</v>
+        <v>-40</v>
       </c>
       <c r="I25" s="14">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J25" s="14">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K25" s="15">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="L25" s="15">
-        <v>-25.333333333333</v>
+        <v>-27.710843373494</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E26" s="15">
-        <v>-18.181818181818</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="F26" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G26" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H26" s="15">
-        <v>-10.714285714285</v>
+        <v>-27.419354838709</v>
       </c>
       <c r="I26" s="14">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="J26" s="14">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="K26" s="15">
-        <v>-7.614213197969</v>
+        <v>-11.467889908256</v>
       </c>
       <c r="L26" s="15">
-        <v>-9.900990099009</v>
+        <v>-11.872146118721</v>
       </c>
       <c r="M26" s="15">
-        <v>52.941176470588</v>
+        <v>49.612403100775</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,22 +1397,22 @@
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
+        <v>-25</v>
+      </c>
+      <c r="I27" s="14">
+        <v>9</v>
+      </c>
+      <c r="J27" s="14">
+        <v>17</v>
+      </c>
+      <c r="K27" s="15">
+        <v>-47.058823529411</v>
+      </c>
+      <c r="L27" s="15">
         <v>0</v>
-      </c>
-      <c r="I27" s="14">
-        <v>8</v>
-      </c>
-      <c r="J27" s="14">
-        <v>16</v>
-      </c>
-      <c r="K27" s="15">
-        <v>-50</v>
-      </c>
-      <c r="L27" s="15">
-        <v>-11.111111111111</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-83.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>-40</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="L28" s="15">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,13 +1476,13 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I29" s="14">
         <v>6</v>
@@ -1500,15 +1500,15 @@
         <v>100</v>
       </c>
       <c r="N29" s="15">
-        <v>-75</v>
+        <v>-76.923076923076</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,13 +1517,13 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
@@ -1541,7 +1541,7 @@
         <v>66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-75</v>
+        <v>-76.190476190476</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,20 +1551,20 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>

--- a/data/source/weekly/cs-en-us-060pct.xlsx
+++ b/data/source/weekly/cs-en-us-060pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -873,10 +873,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
         <v>0</v>
@@ -890,16 +890,16 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>22</v>
-      </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
@@ -923,7 +923,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N15" s="15">
         <v>14.285714285714</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>5</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="E16" s="15">
+        <v>150</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="I16" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J16" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K16" s="15">
-        <v>20.588235294117</v>
+        <v>30.555555555555</v>
       </c>
       <c r="L16" s="15">
-        <v>-12.765957446808</v>
+        <v>-6</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.101265822784</v>
+        <v>-45.977011494252</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.066246056782</v>
+        <v>-86.257309941520</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G17" s="14">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H17" s="15">
-        <v>-21.951219512195</v>
+        <v>2.564102564102</v>
       </c>
       <c r="I17" s="14">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="J17" s="14">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="K17" s="15">
-        <v>27.826086956521</v>
+        <v>22.834645669291</v>
       </c>
       <c r="L17" s="15">
-        <v>34.862385321100</v>
+        <v>34.482758620689</v>
       </c>
       <c r="M17" s="15">
-        <v>234.090909090909</v>
+        <v>218.367346938776</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.807860262008</v>
+        <v>-35.269709543568</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>57.142857142857</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J18" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K18" s="15">
-        <v>-2.631578947368</v>
+        <v>-2.439024390243</v>
       </c>
       <c r="L18" s="15">
-        <v>54.166666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-11.904761904761</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.615384615384</v>
+        <v>-88.439306358381</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-36.363636363636</v>
+        <v>-37.5</v>
       </c>
       <c r="F19" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>28</v>
+        <v>17.241379310344</v>
       </c>
       <c r="I19" s="14">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="J19" s="14">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="K19" s="15">
-        <v>15.116279069767</v>
+        <v>12.765957446808</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.476635514018</v>
+        <v>-7.826086956521</v>
       </c>
       <c r="M19" s="15">
-        <v>-25.563909774436</v>
+        <v>-25.352112676056</v>
       </c>
       <c r="N19" s="15">
-        <v>-41.764705882352</v>
+        <v>-41.436464088397</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="15">
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>-50</v>
+        <v>-10</v>
       </c>
       <c r="I20" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J20" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K20" s="15">
-        <v>-20</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="L20" s="15">
-        <v>-22.580645161290</v>
+        <v>-20.588235294117</v>
       </c>
       <c r="M20" s="15">
-        <v>-27.272727272727</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.162393162393</v>
+        <v>-92.622950819672</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,81 +1139,81 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>-22.580645161290</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="G21" s="17">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.020408163265</v>
+        <v>8.910891089108</v>
       </c>
       <c r="I21" s="17">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="J21" s="17">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="K21" s="18">
-        <v>11.214953271028</v>
+        <v>10.632183908046</v>
       </c>
       <c r="L21" s="18">
-        <v>10.526315789473</v>
+        <v>10</v>
       </c>
       <c r="M21" s="18">
-        <v>7.530120481927</v>
+        <v>7.242339832869</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.644886363636</v>
+        <v>-74.195710455764</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
         <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
+        <v>14</v>
+      </c>
+      <c r="J22" s="14">
         <v>13</v>
       </c>
-      <c r="J22" s="14">
-        <v>11</v>
-      </c>
       <c r="K22" s="15">
-        <v>18.181818181818</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L22" s="15">
-        <v>85.714285714285</v>
+        <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>-13.333333333333</v>
+        <v>-12.5</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1224,10 +1224,10 @@
         <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-60</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
         <v>13</v>
@@ -1239,22 +1239,22 @@
         <v>18.181818181818</v>
       </c>
       <c r="I23" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J23" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K23" s="15">
-        <v>12.5</v>
+        <v>11.627906976744</v>
       </c>
       <c r="L23" s="15">
-        <v>-10</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M23" s="15">
-        <v>87.5</v>
+        <v>84.615384615384</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-5.555555555555</v>
+        <v>10.526315789473</v>
       </c>
       <c r="F24" s="14">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G24" s="14">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>-4.938271604938</v>
       </c>
       <c r="I24" s="14">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="J24" s="14">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.293706293706</v>
+        <v>-5.573770491803</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.219178082191</v>
+        <v>-6.796116504854</v>
       </c>
       <c r="M24" s="15">
-        <v>-12.131147540983</v>
+        <v>-10.835913312693</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>3</v>
+      </c>
+      <c r="D25" s="14">
         <v>4</v>
       </c>
-      <c r="D25" s="14">
-        <v>10</v>
-      </c>
       <c r="E25" s="15">
-        <v>-60</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H25" s="15">
-        <v>-40</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I25" s="14">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J25" s="14">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K25" s="15">
         <v>-25</v>
       </c>
       <c r="L25" s="15">
-        <v>-27.710843373494</v>
+        <v>-28.409090909090</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,54 +1344,54 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-47.619047619047</v>
+        <v>77.777777777777</v>
       </c>
       <c r="F26" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G26" s="14">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H26" s="15">
-        <v>-27.419354838709</v>
+        <v>-20</v>
       </c>
       <c r="I26" s="14">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="J26" s="14">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.467889908256</v>
+        <v>-7.488986784140</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.872146118721</v>
+        <v>-12.133891213389</v>
       </c>
       <c r="M26" s="15">
-        <v>49.612403100775</v>
+        <v>47.887323943662</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
@@ -1412,54 +1412,54 @@
         <v>-47.058823529411</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>4</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
-      </c>
-      <c r="F28" s="14">
-        <v>2</v>
-      </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="I28" s="14">
         <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K28" s="15">
-        <v>-38.095238095238</v>
+        <v>-48</v>
       </c>
       <c r="L28" s="15">
         <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>6</v>
       </c>
       <c r="J29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L29" s="15">
         <v>500</v>
@@ -1500,7 +1500,7 @@
         <v>100</v>
       </c>
       <c r="N29" s="15">
-        <v>-76.923076923076</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
       </c>
       <c r="J30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L30" s="15">
         <v>400</v>
@@ -1541,7 +1541,7 @@
         <v>66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-76.190476190476</v>
+        <v>-77.272727272727</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,16 +1555,16 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="14">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
@@ -1576,13 +1576,13 @@
         <v>-57.142857142857</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33" s="15">
         <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>52</v>

--- a/data/source/weekly/cs-en-us-060pct.xlsx
+++ b/data/source/weekly/cs-en-us-060pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -885,48 +885,48 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
         <v>22</v>
+      </c>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K15" s="15">
-        <v>-50</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>22</v>
+        <v>80</v>
+      </c>
+      <c r="M15" s="15">
+        <v>800</v>
       </c>
       <c r="N15" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>150</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>100</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J16" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K16" s="15">
-        <v>30.555555555555</v>
+        <v>22.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-6</v>
+        <v>-7.547169811320</v>
       </c>
       <c r="M16" s="15">
-        <v>-45.977011494252</v>
+        <v>-46.739130434782</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.257309941520</v>
+        <v>-86.274509803921</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15">
-        <v>-8.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G17" s="14">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H17" s="15">
-        <v>2.564102564102</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I17" s="14">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="J17" s="14">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="K17" s="15">
-        <v>22.834645669291</v>
+        <v>14.685314685314</v>
       </c>
       <c r="L17" s="15">
-        <v>34.482758620689</v>
+        <v>36.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>218.367346938776</v>
+        <v>221.56862745098</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.269709543568</v>
+        <v>-36.679536679536</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I18" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J18" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K18" s="15">
-        <v>-2.439024390243</v>
+        <v>-2.380952380952</v>
       </c>
       <c r="L18" s="15">
-        <v>33.333333333333</v>
+        <v>32.258064516129</v>
       </c>
       <c r="M18" s="15">
-        <v>-11.111111111111</v>
+        <v>-18</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.439306358381</v>
+        <v>-88.828337874659</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>7</v>
+      </c>
+      <c r="D19" s="14">
         <v>5</v>
       </c>
-      <c r="D19" s="14">
-        <v>8</v>
-      </c>
       <c r="E19" s="15">
-        <v>-37.5</v>
+        <v>40</v>
       </c>
       <c r="F19" s="14">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G19" s="14">
         <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>17.241379310344</v>
+        <v>3.448275862068</v>
       </c>
       <c r="I19" s="14">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J19" s="14">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="K19" s="15">
-        <v>12.765957446808</v>
+        <v>15.151515151515</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.826086956521</v>
+        <v>-4.201680672268</v>
       </c>
       <c r="M19" s="15">
-        <v>-25.352112676056</v>
+        <v>-24</v>
       </c>
       <c r="N19" s="15">
-        <v>-41.436464088397</v>
+        <v>-41.538461538461</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>-10</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I20" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J20" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K20" s="15">
-        <v>-12.903225806451</v>
+        <v>-20</v>
       </c>
       <c r="L20" s="15">
-        <v>-20.588235294117</v>
+        <v>-24.324324324324</v>
       </c>
       <c r="M20" s="15">
-        <v>-22.857142857142</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.622950819672</v>
+        <v>-92.513368983957</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="F21" s="17">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="G21" s="17">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H21" s="18">
-        <v>8.910891089108</v>
+        <v>-10.377358490566</v>
       </c>
       <c r="I21" s="17">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="J21" s="17">
-        <v>348</v>
+        <v>379</v>
       </c>
       <c r="K21" s="18">
-        <v>10.632183908046</v>
+        <v>7.124010554089</v>
       </c>
       <c r="L21" s="18">
-        <v>10</v>
+        <v>10.928961748633</v>
       </c>
       <c r="M21" s="18">
-        <v>7.242339832869</v>
+        <v>6.005221932114</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.195710455764</v>
+        <v>-74.156588160407</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,28 +1192,28 @@
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
       <c r="I22" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J22" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K22" s="15">
-        <v>7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="M22" s="15">
-        <v>-12.5</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1224,37 +1224,37 @@
         <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15">
-        <v>-33.333333333333</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F23" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G23" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H23" s="15">
-        <v>18.181818181818</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="I23" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J23" s="14">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="K23" s="15">
-        <v>11.627906976744</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="L23" s="15">
-        <v>-7.692307692307</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="M23" s="15">
-        <v>84.615384615384</v>
+        <v>72.413793103448</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>10.526315789473</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H24" s="15">
-        <v>-4.938271604938</v>
+        <v>-5.952380952380</v>
       </c>
       <c r="I24" s="14">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="J24" s="14">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="K24" s="15">
-        <v>-5.573770491803</v>
+        <v>-6.990881458966</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.796116504854</v>
+        <v>-6.422018348623</v>
       </c>
       <c r="M24" s="15">
-        <v>-10.835913312693</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>5</v>
+      </c>
+      <c r="D25" s="14">
         <v>3</v>
       </c>
-      <c r="D25" s="14">
-        <v>4</v>
-      </c>
       <c r="E25" s="15">
-        <v>-25</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H25" s="15">
-        <v>-46.153846153846</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I25" s="14">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J25" s="14">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K25" s="15">
-        <v>-25</v>
+        <v>-21.839080459770</v>
       </c>
       <c r="L25" s="15">
-        <v>-28.409090909090</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,122 +1344,122 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>13</v>
+      </c>
+      <c r="D26" s="14">
         <v>16</v>
       </c>
-      <c r="D26" s="14">
-        <v>9</v>
-      </c>
       <c r="E26" s="15">
-        <v>77.777777777777</v>
+        <v>-18.75</v>
       </c>
       <c r="F26" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G26" s="14">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H26" s="15">
-        <v>-20</v>
+        <v>-12.280701754386</v>
       </c>
       <c r="I26" s="14">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="J26" s="14">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="K26" s="15">
-        <v>-7.488986784140</v>
+        <v>-8.230452674897</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.133891213389</v>
+        <v>-11.857707509881</v>
       </c>
       <c r="M26" s="15">
-        <v>47.887323943662</v>
+        <v>44.805194805194</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>22</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K27" s="15">
-        <v>-47.058823529411</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L27" s="15">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>3</v>
       </c>
       <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>200</v>
+      </c>
+      <c r="F28" s="14">
         <v>4</v>
       </c>
-      <c r="E28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>1</v>
-      </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-80</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J28" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K28" s="15">
-        <v>-48</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1476,22 +1476,22 @@
         <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>6</v>
       </c>
       <c r="J29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L29" s="15">
         <v>500</v>
@@ -1500,7 +1500,7 @@
         <v>100</v>
       </c>
       <c r="N29" s="15">
-        <v>-77.777777777777</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,22 +1517,22 @@
         <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
       </c>
       <c r="J30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
         <v>400</v>
@@ -1541,7 +1541,7 @@
         <v>66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-77.272727272727</v>
+        <v>-79.166666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1576,13 +1576,13 @@
         <v>-57.142857142857</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L33" s="15">
         <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>52</v>
